--- a/output/full_scan/batch_seq1_2026-08-24.xlsx
+++ b/output/full_scan/batch_seq1_2026-08-24.xlsx
@@ -5520,7 +5520,7 @@
         <v/>
       </c>
       <c r="D96" s="2" t="n">
-        <v>239.4084736420182</v>
+        <v>239.4084736420181</v>
       </c>
       <c r="E96" s="2" t="n">
         <v>8.33</v>
